--- a/Estoque/Estoque 05.2026.xlsx
+++ b/Estoque/Estoque 05.2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Estoque\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03355EAE-A0FA-4045-9FC3-38336D31BFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90F0289-25A8-43EC-A70E-07394646BCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8E53B96B-8C82-452A-AAB2-5E3C25B6EC39}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t xml:space="preserve">Fazenda Vera Cruz - Furnas </t>
   </si>
@@ -129,6 +129,18 @@
   </si>
   <si>
     <t>PREÇO/KG</t>
+  </si>
+  <si>
+    <t>QTDE</t>
+  </si>
+  <si>
+    <t>CUSTO MÉDIO</t>
+  </si>
+  <si>
+    <t>MACHO RECRIA</t>
+  </si>
+  <si>
+    <t>FEMEA RECRIA</t>
   </si>
 </sst>
 </file>
@@ -192,12 +204,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,6 +553,7 @@
     <col min="4" max="4" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -598,16 +612,9 @@
       <c r="E3" s="3">
         <v>6728.8666585164146</v>
       </c>
-      <c r="G3" s="4">
-        <v>30</v>
-      </c>
-      <c r="H3" s="4">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4">
-        <f>G3/H3</f>
-        <v>15</v>
-      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -680,15 +687,15 @@
       <c r="E7" s="3">
         <v>3347.9099158386416</v>
       </c>
-      <c r="G7" s="4">
-        <v>100</v>
-      </c>
-      <c r="H7" s="4">
-        <v>5</v>
-      </c>
-      <c r="I7" s="4">
-        <f>G7/H7</f>
-        <v>20</v>
+      <c r="G7" s="3">
+        <v>5351514</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3020613.35</v>
+      </c>
+      <c r="I7" s="3">
+        <f>H7/G7</f>
+        <v>0.56444089467018121</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -750,6 +757,15 @@
       <c r="E11" s="3">
         <v>5284.6797286452602</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -759,6 +775,15 @@
         <f>1072-2-3-3</f>
         <v>1064</v>
       </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="5">
+        <v>19705</v>
+      </c>
+      <c r="I12" s="5">
+        <v>4267.8936828367932</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -767,6 +792,15 @@
       <c r="B13" s="4">
         <f>254</f>
         <v>254</v>
+      </c>
+      <c r="G13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="5">
+        <v>4278</v>
+      </c>
+      <c r="I13" s="5">
+        <v>3553.4365202112817</v>
       </c>
     </row>
   </sheetData>
